--- a/sports_forms/002_membership_application_form--sports_forms.xlsx
+++ b/sports_forms/002_membership_application_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'soccer'}</t>
+          <t>soccer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'soccer'}</t>
+          <t>soccer</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'basketball'}</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'basketball'}</t>
+          <t>basketball</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'baseball'}</t>
+          <t>baseball</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'baseball'}</t>
+          <t>baseball</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'football'}</t>
+          <t>football</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'football'}</t>
+          <t>football</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'team'}</t>
+          <t>team</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'club'}</t>
+          <t>club</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'club'}</t>
+          <t>club</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'none'}</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'family'}</t>
+          <t>family</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sports_forms'}</t>
+          <t>sports_forms</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'sports forms'}</t>
+          <t>sports forms</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'entrepreneur_forms'}</t>
+          <t>entrepreneur_forms</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'entrepreneur forms'}</t>
+          <t>entrepreneur forms</t>
         </is>
       </c>
     </row>
